--- a/PM_업무관리_대시보드.xlsx
+++ b/PM_업무관리_대시보드.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="StatusList">설정!$A$4:$A$6</definedName>
     <definedName name="PriorityList">설정!$B$4:$B$6</definedName>
-    <definedName name="MemberList">설정!$C$4:$C$13</definedName>
+    <definedName name="MemberList">OFFSET(설정!$C$4,0,0,MAX(1,COUNTA(설정!$C$4:$C$13)),1)</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'업무목록'!$A$1:$K$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -153,7 +153,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -168,11 +168,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000CA30C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -282,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -302,55 +297,55 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="11" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="11" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="12" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="12" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="13" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="13" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="14" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="15" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -389,9 +384,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -986,7 +978,7 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="2340000"/>
@@ -1008,7 +1000,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2880000" cy="2340000"/>
@@ -1030,7 +1022,7 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2340000"/>
@@ -1341,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B35"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1475,7 +1467,7 @@
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 마감일이 지났는데 Done이 아닌 업무 → 행 전체가 붉게 표시되고 D-Day에 '⚠ n일 지연'</t>
+          <t xml:space="preserve">   · 마감일이 지났는데 Done이 아닌 업무 → 행이 붉게 표시되고(상태·우선순위 칩은 원래 색 유지) D-Day에 '⚠ n일 지연'</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1505,7 @@
     <row r="28" ht="18" customHeight="1">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   초록색 담당자 칸(C4~C13)에서 이름을 바꾸거나 추가하세요. 최대 10명까지 가능합니다.</t>
+          <t xml:space="preserve">   초록색 담당자 칸(C4~C13)에 위에서부터 빈칸 없이 이름을 입력하세요. 최대 10명까지 가능합니다.</t>
         </is>
       </c>
     </row>
@@ -1535,28 +1527,42 @@
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   · 업무는 200행까지 서식과 자동 수식이 미리 적용되어 있습니다. 더 필요하면 마지막 행을 복사해 아래로 붙여넣으세요.</t>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 업무는 200건(2~201행)까지 지원합니다. 그 아래(202행부터)에 입력하면 대시보드·칸반에 반영되지 않으니 주의하세요.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · 칸반보드는 각 열에서 위에서부터 30개까지 표시합니다.</t>
+          <t xml:space="preserve">   · 새 업무는 목록 끝의 빈 행에 이어서 입력하세요. 중간에 행을 삽입했다면 바로 위 행 전체를 복사해</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   · D-Day와 지연 표시는 파일을 여는 시점의 '오늘' 날짜 기준으로 자동 계산됩니다.</t>
+          <t xml:space="preserve">     삽입한 행에 붙여넣으세요(숨겨진 자동 수식이 함께 복사됩니다). 안 하면 칸반보드에서 그 업무가 빠질 수 있습니다.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · 칸반보드는 각 열에서 위에서부터 30개까지 표시합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   · D-Day와 지연 표시는 파일을 여는 시점의 '오늘' 날짜 기준으로 자동 계산됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">   · 처음에 들어 있는 예시 업무 12건은 자유롭게 지우고 사용하세요.</t>
         </is>
@@ -1689,22 +1695,22 @@
       </c>
       <c r="C4" s="14" t="n"/>
       <c r="D4" s="15">
-        <f>COUNTIF(업무목록!$F$2:$F$201,"To Do")</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"To Do")</f>
         <v/>
       </c>
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="16">
-        <f>COUNTIF(업무목록!$F$2:$F$201,"Doing")</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"Doing")</f>
         <v/>
       </c>
       <c r="G4" s="14" t="n"/>
       <c r="H4" s="17">
-        <f>COUNTIF(업무목록!$F$2:$F$201,"Done")</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"Done")</f>
         <v/>
       </c>
       <c r="I4" s="14" t="n"/>
       <c r="J4" s="18">
-        <f>IFERROR(COUNTIF(업무목록!$F$2:$F$201,"Done")/COUNTIF(업무목록!$B$2:$B$201,"&lt;&gt;"),0)</f>
+        <f>IFERROR(COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"Done")/COUNTIF(업무목록!$B$2:$B$201,"&lt;&gt;"),0)</f>
         <v/>
       </c>
       <c r="K4" s="14" t="n"/>
@@ -1859,7 +1865,7 @@
         </is>
       </c>
       <c r="C9" s="22">
-        <f>COUNTIF(업무목록!$F$2:$F$201,$B9)</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,$B9)</f>
         <v/>
       </c>
       <c r="D9" s="7" t="n"/>
@@ -1869,7 +1875,7 @@
         </is>
       </c>
       <c r="F9" s="22">
-        <f>COUNTIF(업무목록!$E$2:$E$201,$E9)</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$E$2:$E$201,$E9)</f>
         <v/>
       </c>
       <c r="G9" s="7" t="n"/>
@@ -1878,15 +1884,15 @@
         <v/>
       </c>
       <c r="I9" s="22">
-        <f>IF($H9="","",COUNTIFS(업무목록!$D$2:$D$201,$H9,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H9="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H9,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J9" s="22">
-        <f>IF($H9="","",COUNTIFS(업무목록!$D$2:$D$201,$H9,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H9="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H9,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K9" s="22">
-        <f>IF($H9="","",COUNTIFS(업무목록!$D$2:$D$201,$H9,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H9="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H9,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L9" s="22">
@@ -1911,7 +1917,7 @@
         </is>
       </c>
       <c r="C10" s="22">
-        <f>COUNTIF(업무목록!$F$2:$F$201,$B10)</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,$B10)</f>
         <v/>
       </c>
       <c r="D10" s="7" t="n"/>
@@ -1921,7 +1927,7 @@
         </is>
       </c>
       <c r="F10" s="22">
-        <f>COUNTIF(업무목록!$E$2:$E$201,$E10)</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$E$2:$E$201,$E10)</f>
         <v/>
       </c>
       <c r="G10" s="7" t="n"/>
@@ -1930,15 +1936,15 @@
         <v/>
       </c>
       <c r="I10" s="22">
-        <f>IF($H10="","",COUNTIFS(업무목록!$D$2:$D$201,$H10,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H10="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H10,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J10" s="22">
-        <f>IF($H10="","",COUNTIFS(업무목록!$D$2:$D$201,$H10,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H10="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H10,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K10" s="22">
-        <f>IF($H10="","",COUNTIFS(업무목록!$D$2:$D$201,$H10,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H10="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H10,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L10" s="22">
@@ -1963,7 +1969,7 @@
         </is>
       </c>
       <c r="C11" s="22">
-        <f>COUNTIF(업무목록!$F$2:$F$201,$B11)</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,$B11)</f>
         <v/>
       </c>
       <c r="D11" s="7" t="n"/>
@@ -1973,7 +1979,7 @@
         </is>
       </c>
       <c r="F11" s="22">
-        <f>COUNTIF(업무목록!$E$2:$E$201,$E11)</f>
+        <f>COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$E$2:$E$201,$E11)</f>
         <v/>
       </c>
       <c r="G11" s="7" t="n"/>
@@ -1982,15 +1988,15 @@
         <v/>
       </c>
       <c r="I11" s="22">
-        <f>IF($H11="","",COUNTIFS(업무목록!$D$2:$D$201,$H11,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H11="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H11,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J11" s="22">
-        <f>IF($H11="","",COUNTIFS(업무목록!$D$2:$D$201,$H11,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H11="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H11,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K11" s="22">
-        <f>IF($H11="","",COUNTIFS(업무목록!$D$2:$D$201,$H11,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H11="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H11,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L11" s="22">
@@ -2020,15 +2026,15 @@
         <v/>
       </c>
       <c r="I12" s="22">
-        <f>IF($H12="","",COUNTIFS(업무목록!$D$2:$D$201,$H12,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H12="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H12,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J12" s="22">
-        <f>IF($H12="","",COUNTIFS(업무목록!$D$2:$D$201,$H12,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H12="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H12,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K12" s="22">
-        <f>IF($H12="","",COUNTIFS(업무목록!$D$2:$D$201,$H12,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H12="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H12,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L12" s="22">
@@ -2058,15 +2064,15 @@
         <v/>
       </c>
       <c r="I13" s="22">
-        <f>IF($H13="","",COUNTIFS(업무목록!$D$2:$D$201,$H13,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H13="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H13,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J13" s="22">
-        <f>IF($H13="","",COUNTIFS(업무목록!$D$2:$D$201,$H13,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H13="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H13,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K13" s="22">
-        <f>IF($H13="","",COUNTIFS(업무목록!$D$2:$D$201,$H13,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H13="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H13,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L13" s="22">
@@ -2096,15 +2102,15 @@
         <v/>
       </c>
       <c r="I14" s="22">
-        <f>IF($H14="","",COUNTIFS(업무목록!$D$2:$D$201,$H14,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H14="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H14,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J14" s="22">
-        <f>IF($H14="","",COUNTIFS(업무목록!$D$2:$D$201,$H14,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H14="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H14,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K14" s="22">
-        <f>IF($H14="","",COUNTIFS(업무목록!$D$2:$D$201,$H14,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H14="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H14,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L14" s="22">
@@ -2134,15 +2140,15 @@
         <v/>
       </c>
       <c r="I15" s="22">
-        <f>IF($H15="","",COUNTIFS(업무목록!$D$2:$D$201,$H15,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H15="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H15,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J15" s="22">
-        <f>IF($H15="","",COUNTIFS(업무목록!$D$2:$D$201,$H15,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H15="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H15,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K15" s="22">
-        <f>IF($H15="","",COUNTIFS(업무목록!$D$2:$D$201,$H15,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H15="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H15,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L15" s="22">
@@ -2172,15 +2178,15 @@
         <v/>
       </c>
       <c r="I16" s="22">
-        <f>IF($H16="","",COUNTIFS(업무목록!$D$2:$D$201,$H16,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H16="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H16,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J16" s="22">
-        <f>IF($H16="","",COUNTIFS(업무목록!$D$2:$D$201,$H16,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H16="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H16,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K16" s="22">
-        <f>IF($H16="","",COUNTIFS(업무목록!$D$2:$D$201,$H16,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H16="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H16,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L16" s="22">
@@ -2210,15 +2216,15 @@
         <v/>
       </c>
       <c r="I17" s="22">
-        <f>IF($H17="","",COUNTIFS(업무목록!$D$2:$D$201,$H17,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H17="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H17,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J17" s="22">
-        <f>IF($H17="","",COUNTIFS(업무목록!$D$2:$D$201,$H17,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H17="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H17,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K17" s="22">
-        <f>IF($H17="","",COUNTIFS(업무목록!$D$2:$D$201,$H17,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H17="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H17,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L17" s="22">
@@ -2248,15 +2254,15 @@
         <v/>
       </c>
       <c r="I18" s="22">
-        <f>IF($H18="","",COUNTIFS(업무목록!$D$2:$D$201,$H18,업무목록!$F$2:$F$201,"To Do"))</f>
+        <f>IF($H18="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H18,업무목록!$F$2:$F$201,"To Do"))</f>
         <v/>
       </c>
       <c r="J18" s="22">
-        <f>IF($H18="","",COUNTIFS(업무목록!$D$2:$D$201,$H18,업무목록!$F$2:$F$201,"Doing"))</f>
+        <f>IF($H18="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H18,업무목록!$F$2:$F$201,"Doing"))</f>
         <v/>
       </c>
       <c r="K18" s="22">
-        <f>IF($H18="","",COUNTIFS(업무목록!$D$2:$D$201,$H18,업무목록!$F$2:$F$201,"Done"))</f>
+        <f>IF($H18="","",COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$D$2:$D$201,$H18,업무목록!$F$2:$F$201,"Done"))</f>
         <v/>
       </c>
       <c r="L18" s="22">
@@ -2689,15 +2695,15 @@
     </row>
     <row r="4" ht="26" customHeight="1">
       <c r="B4" s="26">
-        <f>"To Do  ("&amp;COUNTIF(업무목록!$F$2:$F$201,"To Do")&amp;"건)"</f>
+        <f>"To Do  ("&amp;COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"To Do")&amp;"건)"</f>
         <v/>
       </c>
       <c r="D4" s="27">
-        <f>"Doing  ("&amp;COUNTIF(업무목록!$F$2:$F$201,"Doing")&amp;"건)"</f>
+        <f>"Doing  ("&amp;COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"Doing")&amp;"건)"</f>
         <v/>
       </c>
       <c r="F4" s="28">
-        <f>"Done  ("&amp;COUNTIF(업무목록!$F$2:$F$201,"Done")&amp;"건)"</f>
+        <f>"Done  ("&amp;COUNTIFS(업무목록!$B$2:$B$201,"&lt;&gt;",업무목록!$F$2:$F$201,"Done")&amp;"건)"</f>
         <v/>
       </c>
     </row>
@@ -10770,24 +10776,24 @@
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="42" t="n"/>
+      <c r="C9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="C10" s="42" t="n"/>
+      <c r="C10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="C11" s="42" t="n"/>
+      <c r="C11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="C12" s="42" t="n"/>
+      <c r="C12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="C13" s="42" t="n"/>
+      <c r="C13" s="41" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>※ 담당자는 최대 10명까지(C4~C13). 이름을 바꾸면 업무목록 드롭다운과 대시보드에 바로 반영됩니다.</t>
+          <t>※ 담당자는 초록색 칸(C4~C13)에 위에서부터 빈칸 없이 최대 10명까지 입력하세요. 바꾸면 드롭다운과 대시보드에 바로 반영됩니다.</t>
         </is>
       </c>
     </row>
